--- a/config/replace_title.xlsx
+++ b/config/replace_title.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\python\NLP\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07CDD25F-2DAA-4094-A913-A7B44186DB1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C2443B-D9ED-4E7A-A914-FFB8C6BD8924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-10790" windowWidth="21820" windowHeight="38620" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="标题" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2551" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2559" uniqueCount="455">
   <si>
     <t>原始值</t>
   </si>
@@ -1630,6 +1630,7 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -4069,7 +4070,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D587D47-4BBF-4FD3-8290-8F39DAFD7BEA}">
-  <dimension ref="A1:C268"/>
+  <dimension ref="A1:C270"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="3" width="18.375" customWidth="1"/>
@@ -6963,6 +6964,28 @@
       </c>
       <c r="C268" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A269" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B269" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C269" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A270" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B270" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C270" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6973,7 +6996,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C62E81A4-C419-4CD8-B40A-870B9D16ECD3}">
-  <dimension ref="A1:C265"/>
+  <dimension ref="A1:C267"/>
   <sheetFormatPr defaultColWidth="16" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="31.625" customWidth="1"/>
@@ -9834,6 +9857,28 @@
       </c>
       <c r="C265" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A266" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B266" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C266" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A267" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B267" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C267" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
